--- a/public/flashcards/minna_lesson_16.xlsx
+++ b/public/flashcards/minna_lesson_16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Chat-Website\public\flashcards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8140D8C8-9559-4D98-B437-FF363804EC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD49A98-48A6-478B-9C80-91021515EB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="220">
   <si>
     <t>Hiragana/Katakana</t>
   </si>
@@ -55,9 +55,6 @@
     <t>ขึ้น [รถไฟ], ขี่</t>
   </si>
   <si>
-    <t>￴おります [でんしゃを～]</t>
-  </si>
-  <si>
     <t>降ります [電車を～]</t>
   </si>
   <si>
@@ -76,9 +73,6 @@
     <t>norikaemasu</t>
   </si>
   <si>
-    <t>ต่อรถ, เปลี่ยนรถ</t>
-  </si>
-  <si>
     <t>あびます [シャワーを～]</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>abimasu [shawa- o ~]</t>
   </si>
   <si>
-    <t>อาบ [น้ำฝักบัว]</t>
-  </si>
-  <si>
     <t>いれます</t>
   </si>
   <si>
@@ -112,9 +103,6 @@
     <t>dashimasu</t>
   </si>
   <si>
-    <t>เอาออก, ยื่น, ส่ง</t>
-  </si>
-  <si>
     <t>はいります [だいがくに～]</t>
   </si>
   <si>
@@ -139,18 +127,6 @@
     <t>จบ [การศึกษาจากมหาวิทยาลัย]</t>
   </si>
   <si>
-    <t>やめます [かいしゃを～]</t>
-  </si>
-  <si>
-    <t>辞めます [会社を～]</t>
-  </si>
-  <si>
-    <t>yamemasu [kaisha o ~]</t>
-  </si>
-  <si>
-    <t>ลาออก [จากบริษัท], เลิก</t>
-  </si>
-  <si>
     <t>おします</t>
   </si>
   <si>
@@ -160,9 +136,6 @@
     <t>oshimasu</t>
   </si>
   <si>
-    <t>กด, ผลัก, ดัน</t>
-  </si>
-  <si>
     <t>わかい</t>
   </si>
   <si>
@@ -172,9 +145,6 @@
     <t>wakai</t>
   </si>
   <si>
-    <t>หนุ่มสาว, อายุน้อย</t>
-  </si>
-  <si>
     <t>ながい</t>
   </si>
   <si>
@@ -208,9 +178,6 @@
     <t>akarui</t>
   </si>
   <si>
-    <t>สว่าง, สดใส</t>
-  </si>
-  <si>
     <t>くらい</t>
   </si>
   <si>
@@ -223,30 +190,6 @@
     <t>มืด</t>
   </si>
   <si>
-    <t>せが たかい</t>
-  </si>
-  <si>
-    <t>背が 高い</t>
-  </si>
-  <si>
-    <t>se ga takai</t>
-  </si>
-  <si>
-    <t>ตัวสูง</t>
-  </si>
-  <si>
-    <t>あたまが いい</t>
-  </si>
-  <si>
-    <t>頭が いい</t>
-  </si>
-  <si>
-    <t>atama ga ii</t>
-  </si>
-  <si>
-    <t>ฉลาด, หัวดี</t>
-  </si>
-  <si>
     <t>からだ</t>
   </si>
   <si>
@@ -256,9 +199,6 @@
     <t>karada</t>
   </si>
   <si>
-    <t>ร่างกาย</t>
-  </si>
-  <si>
     <t>あたま</t>
   </si>
   <si>
@@ -268,9 +208,6 @@
     <t>atama</t>
   </si>
   <si>
-    <t>หัว, ศีรษะ</t>
-  </si>
-  <si>
     <t>かみ</t>
   </si>
   <si>
@@ -292,9 +229,6 @@
     <t>kao</t>
   </si>
   <si>
-    <t>หน้า</t>
-  </si>
-  <si>
     <t>め</t>
   </si>
   <si>
@@ -346,9 +280,6 @@
     <t>おなか</t>
   </si>
   <si>
-    <t>お腹</t>
-  </si>
-  <si>
     <t>onaka</t>
   </si>
   <si>
@@ -382,9 +313,6 @@
     <t>jogingu</t>
   </si>
   <si>
-    <t>จ๊อกกิ้ง</t>
-  </si>
-  <si>
     <t>おひきだしですか。</t>
   </si>
   <si>
@@ -478,9 +406,6 @@
     <t>shawa-</t>
   </si>
   <si>
-    <t>น้ำฝักบัว</t>
-  </si>
-  <si>
     <t>みどり</t>
   </si>
   <si>
@@ -490,21 +415,6 @@
     <t>midori</t>
   </si>
   <si>
-    <t>สีเขียว, พื้นที่สีเขียว</t>
-  </si>
-  <si>
-    <t>おてら</t>
-  </si>
-  <si>
-    <t>お寺</t>
-  </si>
-  <si>
-    <t>otera</t>
-  </si>
-  <si>
-    <t>วัด (พุทธ)</t>
-  </si>
-  <si>
     <t>じんじゃ</t>
   </si>
   <si>
@@ -514,33 +424,6 @@
     <t>jinja</t>
   </si>
   <si>
-    <t>ศาลเจ้า (ชินโต)</t>
-  </si>
-  <si>
-    <t>りゅうがくせい</t>
-  </si>
-  <si>
-    <t>留学生</t>
-  </si>
-  <si>
-    <t>ryuugakusei</t>
-  </si>
-  <si>
-    <t>นักเรียนต่างชาติ</t>
-  </si>
-  <si>
-    <t>～ばん</t>
-  </si>
-  <si>
-    <t>～番</t>
-  </si>
-  <si>
-    <t>~ban</t>
-  </si>
-  <si>
-    <t>หมายเลข～, เบอร์～</t>
-  </si>
-  <si>
     <t>どうやって</t>
   </si>
   <si>
@@ -556,23 +439,263 @@
     <t>dono ~</t>
   </si>
   <si>
-    <t>～ไหน (ใช้กับคำนาม)</t>
-  </si>
-  <si>
     <t>[いいえ、] まだまだです。</t>
   </si>
   <si>
     <t>[Iie,] madamada desu.</t>
   </si>
   <si>
-    <t>[ไม่] ยังไม่ถึงขนาดนั้นหรอกครับ/ค่ะ (ถ่อมตัว)</t>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>おります [でんしゃを～]</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>おろします [おかねを～]</t>
+  </si>
+  <si>
+    <t>下ろします [お金を～]</t>
+  </si>
+  <si>
+    <t>oroshimasu [okane o ~]</t>
+  </si>
+  <si>
+    <t>のみます</t>
+  </si>
+  <si>
+    <t>飲みます</t>
+  </si>
+  <si>
+    <t>nomimasu</t>
+  </si>
+  <si>
+    <t>はじめます</t>
+  </si>
+  <si>
+    <t>始めます</t>
+  </si>
+  <si>
+    <t>hajimemasu</t>
+  </si>
+  <si>
+    <t>けんがくします</t>
+  </si>
+  <si>
+    <t>見学します</t>
+  </si>
+  <si>
+    <t>kengakushimasu</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>でんわします</t>
+  </si>
+  <si>
+    <t>電話します</t>
+  </si>
+  <si>
+    <t>denwashimasu</t>
+  </si>
+  <si>
+    <t>はな</t>
+  </si>
+  <si>
+    <t>鼻</t>
+  </si>
+  <si>
+    <t>hana</t>
+  </si>
+  <si>
+    <t>せ</t>
+  </si>
+  <si>
+    <t>背</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>[お] てら</t>
+  </si>
+  <si>
+    <t>[お] 寺</t>
+  </si>
+  <si>
+    <t>[o] tera</t>
+  </si>
+  <si>
+    <t>―ばん</t>
+  </si>
+  <si>
+    <t>―番</t>
+  </si>
+  <si>
+    <t>-ban</t>
+  </si>
+  <si>
+    <t>どれ</t>
+  </si>
+  <si>
+    <t>dore</t>
+  </si>
+  <si>
+    <t>เปลี่ยนรถ, ต่อ (รถไฟ รถเมล์ ฯลฯ)</t>
+  </si>
+  <si>
+    <t>อาบน้ำ [ฝักบัว]</t>
+  </si>
+  <si>
+    <t>เอาออก, ยื่น, ส่ง (รายงาน)</t>
+  </si>
+  <si>
+    <t>ถอน [เงิน], เอาลง</t>
+  </si>
+  <si>
+    <t>กด (ปุ่ม), ผลัก, ดัน</t>
+  </si>
+  <si>
+    <t>ดื่ม (เหล้า)</t>
+  </si>
+  <si>
+    <t>เริ่ม, เริ่มต้น</t>
+  </si>
+  <si>
+    <t>ทัศนศึกษา, เยี่ยมชม</t>
+  </si>
+  <si>
+    <t>โทรศัพท์</t>
+  </si>
+  <si>
+    <t>หนุ่ม, สาว, อายุน้อย</t>
+  </si>
+  <si>
+    <t>สว่าง</t>
+  </si>
+  <si>
+    <t>ร่างกาย, สุขภาพ</t>
+  </si>
+  <si>
+    <t>หัว, ศรีษะ, มันสมอง</t>
+  </si>
+  <si>
+    <t>หน้า, ใบหน้า</t>
+  </si>
+  <si>
+    <t>จมูก</t>
+  </si>
+  <si>
+    <t>(ตัว)สูง, ส่วนสูง</t>
+  </si>
+  <si>
+    <t>จ็อกกิ้ง (~をします:วิ่งจ็อกกิ้ง)</t>
+  </si>
+  <si>
+    <t>การอาบน้ำฝักบัว</t>
+  </si>
+  <si>
+    <t>สีเขียว, พื้นที่สีเขียว, พฤษชาติ</t>
+  </si>
+  <si>
+    <t>วัดพุทธ</t>
+  </si>
+  <si>
+    <t>ศาลเจ้าชินโต</t>
+  </si>
+  <si>
+    <t>หมายเลข―, (รถเมล์)สาย―</t>
+  </si>
+  <si>
+    <t>～ไหน(ใช้กับสิ่งของที่มีจำนวนตั้งแต่สามสิ่งขึ้นไป)</t>
+  </si>
+  <si>
+    <t>อันไหน (ในจำนวนสิ่งของตั้งแต่สามสิ่งขึ้นไป)</t>
+  </si>
+  <si>
+    <t>[ไม่] ยังไม่ขนาดนั้น (แสดงการถ่อมตัวเมื่อได้รับคำชม)</t>
+  </si>
+  <si>
+    <t>จะถอนเงินหรอครับ/คะ</t>
+  </si>
+  <si>
+    <t>ต่อไป, ขั้นต่อไป</t>
+  </si>
+  <si>
+    <t>บัตรเอทีเอ็ม</t>
+  </si>
+  <si>
+    <t>การยืนยัน (～します:ยืนยัน)</t>
+  </si>
+  <si>
+    <t>JR</t>
+  </si>
+  <si>
+    <t>รถไฟ JR</t>
+  </si>
+  <si>
+    <t>ゆきまつり</t>
+  </si>
+  <si>
+    <t>雪祭り</t>
+  </si>
+  <si>
+    <t>yukimatsuri</t>
+  </si>
+  <si>
+    <t>เทศกาลหิมะ</t>
+  </si>
+  <si>
+    <t>バンドン</t>
+  </si>
+  <si>
+    <t>bandon</t>
+  </si>
+  <si>
+    <t>บันดุง (อยู่ในประเทศอินโดนีเซีย)</t>
+  </si>
+  <si>
+    <t>フランケン</t>
+  </si>
+  <si>
+    <t>furanken</t>
+  </si>
+  <si>
+    <t>ฟรังเคน (อยู่ในประเทศเยอรมนี)</t>
+  </si>
+  <si>
+    <t>ベラクルス</t>
+  </si>
+  <si>
+    <t>berakurusu</t>
+  </si>
+  <si>
+    <t>เวรากรูซ (อยู่ในประเทศเม็กซิโก)</t>
+  </si>
+  <si>
+    <t>うめだ</t>
+  </si>
+  <si>
+    <t>梅田</t>
+  </si>
+  <si>
+    <t>umeda</t>
+  </si>
+  <si>
+    <t>ชื่อเมืองในโอซาก้า</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -593,6 +716,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -602,7 +736,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -625,17 +759,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -917,8 +1078,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
@@ -926,644 +1087,943 @@
     <col min="4" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A8" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="27" thickBot="1">
+      <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D11" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A12" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A13" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A15" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A16" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D16" s="3"/>
+      <c r="E16" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A21" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D22" s="3"/>
+      <c r="E22" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A23" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A24" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A26" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A27" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A28" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A29" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A30" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="D30" s="3"/>
+      <c r="E30" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A31" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="D31" s="3"/>
+      <c r="E31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A33" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D33" s="3"/>
+      <c r="E33" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A34" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D34" s="3"/>
+      <c r="E34" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A35" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A36" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A37" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A38" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A39" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A40" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A41" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A42" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A43" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A44" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="B44" s="6" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="C44" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D44" s="3"/>
+      <c r="E44" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A45" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="B45" s="3"/>
+      <c r="C45" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="D45" s="3"/>
+      <c r="E45" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="2" t="s">
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A46" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A47" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="B47" s="3"/>
+      <c r="C47" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="D47" s="3"/>
+      <c r="E47" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A48" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B48" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C48" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D48" s="3"/>
+      <c r="E48" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="49" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A49" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2" t="s">
+      <c r="B49" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="D49" s="3"/>
+      <c r="E49" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2" t="s">
+    </row>
+    <row r="50" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A50" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="B50" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="C50" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D50" s="3"/>
+      <c r="E50" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A51" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="B51" s="3"/>
+      <c r="C51" s="6" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="D51" s="3"/>
+      <c r="E51" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>146</v>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A52" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A53" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A54" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A55" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="C55" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A56" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" thickBot="1">
+      <c r="A57" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -1575,7 +2035,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D910CF-2294-4D9D-A95D-43F979346F87}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.140625" customWidth="1"/>
@@ -1583,7 +2043,7 @@
     <col min="4" max="4" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1597,110 +2057,110 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="29.25" thickBot="1">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="29.25" thickBot="1">
       <c r="A4" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="29.25" thickBot="1">
       <c r="A5" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1">
       <c r="A6" s="2" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1">
       <c r="A8" s="2" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1">
       <c r="A9" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
